--- a/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_388_R42.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_388_R42.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.043900000000001</v>
+        <v>9.738899999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4968</v>
+        <v>4.3858</v>
       </c>
       <c r="F2" t="n">
-        <v>5.5471</v>
+        <v>5.3531</v>
       </c>
       <c r="G2" t="n">
         <v>9.173299999999999</v>
@@ -610,13 +610,13 @@
         <v>1.5923</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7805</v>
+        <v>1.4755</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6464</v>
+        <v>0.2425</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4269</v>
+        <v>1.233</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.6226</v>
+        <v>8.4682</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0014</v>
+        <v>3.2349</v>
       </c>
       <c r="F3" t="n">
-        <v>5.6213</v>
+        <v>5.2334</v>
       </c>
       <c r="G3" t="n">
         <v>3.6904</v>
@@ -688,13 +688,13 @@
         <v>1.5923</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9322</v>
+        <v>1.7778</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2755</v>
+        <v>0.5089</v>
       </c>
       <c r="U3" t="n">
-        <v>1.6567</v>
+        <v>1.2689</v>
       </c>
       <c r="V3" t="n">
         <v>1.6352</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>8.4259</v>
+        <v>8.047000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>7.5546</v>
+        <v>7.7252</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8712</v>
+        <v>0.3218</v>
       </c>
       <c r="G4" t="n">
         <v>6.1823</v>
@@ -766,13 +766,13 @@
         <v>1.3648</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8787</v>
+        <v>0.4998</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4428</v>
+        <v>-0.2722</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3215</v>
+        <v>0.7721</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. HALL</t>
+          <t>S. MCKISSIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,40 +799,40 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.9115</v>
+        <v>5.5426</v>
       </c>
       <c r="E5" t="n">
-        <v>3.5607</v>
+        <v>3.9287</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3509</v>
+        <v>1.6139</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6164</v>
+        <v>5.1722</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9481000000000001</v>
+        <v>1.8449</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6682</v>
+        <v>3.3273</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2831</v>
+        <v>3.5276</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1713</v>
+        <v>2.2237</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1118</v>
+        <v>1.3038</v>
       </c>
       <c r="M5" t="n">
-        <v>1.3333</v>
+        <v>1.6446</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2232</v>
+        <v>-0.3788</v>
       </c>
       <c r="O5" t="n">
-        <v>1.5565</v>
+        <v>2.0234</v>
       </c>
       <c r="P5" t="n">
         <v>0.4549</v>
@@ -844,28 +844,28 @@
         <v>0.4549</v>
       </c>
       <c r="S5" t="n">
-        <v>2.6818</v>
+        <v>1.0056</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1192</v>
+        <v>0.4011</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5626</v>
+        <v>0.6045</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1583</v>
+        <v>-1.0901</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1583</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.0901</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. MCKISSIC</t>
+          <t>D. HALL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>5.8731</v>
+        <v>4.6274</v>
       </c>
       <c r="E6" t="n">
-        <v>4.1622</v>
+        <v>2.2766</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7109</v>
+        <v>2.3509</v>
       </c>
       <c r="G6" t="n">
-        <v>5.1722</v>
+        <v>2.6164</v>
       </c>
       <c r="H6" t="n">
-        <v>1.8449</v>
+        <v>0.9481000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>3.3273</v>
+        <v>1.6682</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5276</v>
+        <v>1.2831</v>
       </c>
       <c r="K6" t="n">
-        <v>2.2237</v>
+        <v>1.1713</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3038</v>
+        <v>0.1118</v>
       </c>
       <c r="M6" t="n">
-        <v>1.6446</v>
+        <v>1.3333</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3788</v>
+        <v>-0.2232</v>
       </c>
       <c r="O6" t="n">
-        <v>2.0234</v>
+        <v>1.5565</v>
       </c>
       <c r="P6" t="n">
         <v>0.4549</v>
@@ -922,28 +922,28 @@
         <v>0.4549</v>
       </c>
       <c r="S6" t="n">
-        <v>1.336</v>
+        <v>1.3978</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6346000000000001</v>
+        <v>0.8351</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7015</v>
+        <v>0.5626</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0901</v>
+        <v>0.1583</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.1583</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0901</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. JOSEPH</t>
+          <t>T. WALKUP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4081</v>
+        <v>2.0933</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.2163</v>
+        <v>2.3356</v>
       </c>
       <c r="F7" t="n">
-        <v>3.6243</v>
+        <v>-0.2422</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2702</v>
+        <v>2.8841</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3447</v>
+        <v>-0.1002</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0745</v>
+        <v>2.9843</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.5528</v>
+        <v>4.0598</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0709</v>
+        <v>0.3968</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.482</v>
+        <v>3.663</v>
       </c>
       <c r="M7" t="n">
-        <v>1.2827</v>
+        <v>-1.1757</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2738</v>
+        <v>-0.497</v>
       </c>
       <c r="O7" t="n">
-        <v>1.5565</v>
+        <v>-0.6787</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6824</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.5022</v>
+        <v>-1.1374</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8198</v>
+        <v>1.1374</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7255</v>
+        <v>-0.4041</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2036</v>
+        <v>-0.7452</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5219</v>
+        <v>0.3411</v>
       </c>
       <c r="V7" t="n">
-        <v>1.6352</v>
+        <v>-0.3867</v>
       </c>
       <c r="W7" t="n">
-        <v>1.6352</v>
+        <v>0.1583</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.5451</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. WALKUP</t>
+          <t>C. JOSEPH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2045</v>
+        <v>2.0564</v>
       </c>
       <c r="E8" t="n">
-        <v>1.9315</v>
+        <v>-1.6326</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7271</v>
+        <v>3.689</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8841</v>
+        <v>-0.2702</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1002</v>
+        <v>-0.3447</v>
       </c>
       <c r="I8" t="n">
-        <v>2.9843</v>
+        <v>0.0745</v>
       </c>
       <c r="J8" t="n">
-        <v>4.0598</v>
+        <v>-1.5528</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3968</v>
+        <v>-0.0709</v>
       </c>
       <c r="L8" t="n">
-        <v>3.663</v>
+        <v>-1.482</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1757</v>
+        <v>1.2827</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.497</v>
+        <v>-0.2738</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6787</v>
+        <v>1.5565</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.6824</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1374</v>
+        <v>-2.5022</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1374</v>
+        <v>1.8198</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2929</v>
+        <v>1.3738</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.1492</v>
+        <v>0.7873</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1437</v>
+        <v>0.5865</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3867</v>
+        <v>1.6352</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1583</v>
+        <v>1.6352</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5451</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7271</v>
+        <v>-0.6679</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6109</v>
+        <v>-1.584</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8838</v>
+        <v>0.9161</v>
       </c>
       <c r="G9" t="n">
         <v>0.3268</v>
@@ -1156,13 +1156,13 @@
         <v>1.8198</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5603</v>
+        <v>0.6196</v>
       </c>
       <c r="T9" t="n">
-        <v>0.06</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5003</v>
+        <v>0.5327</v>
       </c>
       <c r="V9" t="n">
         <v>-0.9318</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. MILUTINOV</t>
+          <t>K. PAPANIKOLAOU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8336</v>
+        <v>-0.9681999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6543</v>
+        <v>-0.2843</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1794</v>
+        <v>-0.6839</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0649</v>
+        <v>-1.1837</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1545</v>
+        <v>0.0375</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2194</v>
+        <v>-1.2212</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4949</v>
+        <v>1.0984</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3087</v>
+        <v>0.8626</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1863</v>
+        <v>0.2357</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.43</v>
+        <v>-2.2821</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4632</v>
+        <v>-0.8250999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0332</v>
+        <v>-1.4569</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.4549</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.1374</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6824</v>
+        <v>1.1374</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6465</v>
+        <v>0.2155</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0119</v>
+        <v>-0.2453</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6584</v>
+        <v>0.4608</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0901</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0901</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. PAPANIKOLAOU</t>
+          <t>N. MILUTINOV</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9825</v>
+        <v>-1.0851</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2663</v>
+        <v>-0.7441</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7161999999999999</v>
+        <v>-0.341</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.1837</v>
+        <v>0.0649</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0375</v>
+        <v>-0.1545</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.2212</v>
+        <v>0.2194</v>
       </c>
       <c r="J11" t="n">
-        <v>1.0984</v>
+        <v>0.4949</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8626</v>
+        <v>0.3087</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2357</v>
+        <v>0.1863</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.2821</v>
+        <v>-0.43</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8250999999999999</v>
+        <v>-0.4632</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.4569</v>
+        <v>0.0332</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0.4549</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.1374</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1374</v>
+        <v>0.6824</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2012</v>
+        <v>0.3951</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2273</v>
+        <v>-0.1017</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4285</v>
+        <v>0.4968</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.0901</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.0901</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.8727</v>
+        <v>-1.413</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.2634</v>
+        <v>-3.1916</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3907</v>
+        <v>1.7785</v>
       </c>
       <c r="G12" t="n">
         <v>-0.4576</v>
@@ -1390,13 +1390,13 @@
         <v>1.3648</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3784</v>
+        <v>0.8381</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2036</v>
+        <v>0.2755</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1748</v>
+        <v>0.5626</v>
       </c>
       <c r="V12" t="n">
         <v>-1.7935</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.7398</v>
+        <v>-6.6695</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.9255</v>
+        <v>-6.2431</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.8143</v>
+        <v>-0.4264</v>
       </c>
       <c r="G13" t="n">
         <v>-6.6815</v>
@@ -1468,13 +1468,13 @@
         <v>1.3648</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2858</v>
+        <v>-0.2155</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0774</v>
+        <v>-0.395</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2084</v>
+        <v>0.1795</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>28.3339</v>
+        <v>29.7701</v>
       </c>
       <c r="E14" t="n">
-        <v>8.770499999999998</v>
+        <v>10.2071</v>
       </c>
       <c r="F14" t="n">
         <v>19.5632</v>
@@ -1519,7 +1519,7 @@
         <v>17.5418</v>
       </c>
       <c r="J14" t="n">
-        <v>18.7323</v>
+        <v>18.73230000000001</v>
       </c>
       <c r="K14" t="n">
         <v>8.692</v>
@@ -1528,13 +1528,13 @@
         <v>10.04</v>
       </c>
       <c r="M14" t="n">
-        <v>2.785300000000002</v>
+        <v>2.785300000000001</v>
       </c>
       <c r="N14" t="n">
         <v>-4.7164</v>
       </c>
       <c r="O14" t="n">
-        <v>7.501800000000003</v>
+        <v>7.501800000000001</v>
       </c>
       <c r="P14" t="n">
         <v>1.1373</v>
@@ -1546,13 +1546,13 @@
         <v>14.7856</v>
       </c>
       <c r="S14" t="n">
-        <v>7.542399999999999</v>
+        <v>8.978999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.05849999999999977</v>
+        <v>1.3779</v>
       </c>
       <c r="U14" t="n">
-        <v>7.601</v>
+        <v>7.6011</v>
       </c>
       <c r="V14" t="n">
         <v>-1.8635</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2669</v>
+        <v>1.9307</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6924</v>
+        <v>1.2916</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5745</v>
+        <v>0.6391</v>
       </c>
       <c r="G15" t="n">
         <v>0.9215</v>
@@ -1624,13 +1624,13 @@
         <v>1.3648</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1862</v>
+        <v>0.85</v>
       </c>
       <c r="T15" t="n">
-        <v>1.7601</v>
+        <v>0.3593</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4261</v>
+        <v>0.4907</v>
       </c>
       <c r="V15" t="n">
         <v>0.3867</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1194</v>
+        <v>-0.2415</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.0417</v>
+        <v>-2.8083</v>
       </c>
       <c r="F16" t="n">
-        <v>2.9223</v>
+        <v>2.5668</v>
       </c>
       <c r="G16" t="n">
         <v>0.3452</v>
@@ -1702,13 +1702,13 @@
         <v>2.0473</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9196</v>
+        <v>-1.0417</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7901</v>
+        <v>-0.5566</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1295</v>
+        <v>-0.485</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9330000000000001</v>
+        <v>-1.03</v>
       </c>
       <c r="E17" t="n">
         <v>-0.9937</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0607</v>
+        <v>-0.0362</v>
       </c>
       <c r="G17" t="n">
         <v>-1.012</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.079</v>
+        <v>-0.018</v>
       </c>
       <c r="T17" t="n">
         <v>-0.2155</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2945</v>
+        <v>0.1975</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5343</v>
+        <v>-1.8449</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.8646</v>
+        <v>-2.9813</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3303</v>
+        <v>1.1364</v>
       </c>
       <c r="G18" t="n">
         <v>-1.8034</v>
@@ -1858,13 +1858,13 @@
         <v>2.5022</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9792999999999999</v>
+        <v>-1.29</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0174</v>
+        <v>-1.1342</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0381</v>
+        <v>-0.1559</v>
       </c>
       <c r="V18" t="n">
         <v>1.2485</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. JAMES</t>
+          <t>A. DIALLO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.909</v>
+        <v>-3.4251</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5581</v>
+        <v>-1.8389</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.3509</v>
+        <v>-1.5862</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.2239</v>
+        <v>-3.3566</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.3472</v>
+        <v>0.0345</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8767</v>
+        <v>-3.3911</v>
       </c>
       <c r="J19" t="n">
-        <v>1.0032</v>
+        <v>-0.7077</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3833</v>
+        <v>0.9815</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3865</v>
+        <v>-1.6892</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.2271</v>
+        <v>-2.6489</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9639</v>
+        <v>-0.947</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.2632</v>
+        <v>-1.7019</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.2747</v>
+        <v>0.9099</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.5022</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2275</v>
+        <v>0.9099</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5004999999999999</v>
+        <v>-0.8201000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1492</v>
+        <v>-1.1312</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6487000000000001</v>
+        <v>0.3112</v>
       </c>
       <c r="V19" t="n">
-        <v>1.0901</v>
+        <v>-0.1583</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0901</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.1583</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. DIALLO</t>
+          <t>J. BLOSSOMGAME</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.9171</v>
+        <v>-3.6056</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0724</v>
+        <v>-0.7166</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8448</v>
+        <v>-2.889</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.3566</v>
+        <v>-2.8777</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0345</v>
+        <v>0.3128</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.3911</v>
+        <v>-3.1905</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7077</v>
+        <v>0.8007</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9815</v>
+        <v>1.7943</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.6892</v>
+        <v>-0.9936</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.6489</v>
+        <v>-3.6783</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.947</v>
+        <v>-1.4815</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.7019</v>
+        <v>-2.1968</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9099</v>
+        <v>1.8198</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9099</v>
+        <v>1.8198</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3121</v>
+        <v>-1.4576</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.3647</v>
+        <v>-1.5173</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0526</v>
+        <v>0.0597</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1583</v>
+        <v>-1.0901</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1583</v>
+        <v>-1.0901</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. BLOSSOMGAME</t>
+          <t>M. JAMES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0851</v>
+        <v>-4.1478</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0668</v>
+        <v>-1.4414</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.0182</v>
+        <v>-2.7064</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.8777</v>
+        <v>-2.2239</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3128</v>
+        <v>-1.3472</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.1905</v>
+        <v>-0.8767</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8007</v>
+        <v>1.0032</v>
       </c>
       <c r="K21" t="n">
-        <v>1.7943</v>
+        <v>-0.3833</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.9936</v>
+        <v>1.3865</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.6783</v>
+        <v>-3.2271</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.4815</v>
+        <v>-0.9639</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.1968</v>
+        <v>-2.2632</v>
       </c>
       <c r="P21" t="n">
-        <v>1.8198</v>
+        <v>-2.2747</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.5022</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8198</v>
+        <v>0.2275</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.9371</v>
+        <v>-0.7393</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.8675</v>
+        <v>-1.0325</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0696</v>
+        <v>0.2932</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0901</v>
+        <v>1.0901</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.0901</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0901</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.8521</v>
+        <v>-4.5163</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.7635</v>
+        <v>-3.8802</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0886</v>
+        <v>-0.6361</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2003</v>
@@ -2170,13 +2170,13 @@
         <v>1.8198</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4461</v>
+        <v>-1.1104</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9456</v>
+        <v>-1.0623</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5006</v>
+        <v>-0.0481</v>
       </c>
       <c r="V22" t="n">
         <v>-0.1583</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.9149</v>
+        <v>-4.5323</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.4613</v>
+        <v>-4.1111</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4535</v>
+        <v>-0.4212</v>
       </c>
       <c r="G23" t="n">
         <v>-4.973</v>
@@ -2248,13 +2248,13 @@
         <v>1.5923</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2595</v>
+        <v>-0.8769</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9337</v>
+        <v>-0.5835</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3257</v>
+        <v>-0.2934</v>
       </c>
       <c r="V23" t="n">
         <v>1.0901</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.3359</v>
+        <v>-6.921</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.0687</v>
+        <v>-3.7185</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.2672</v>
+        <v>-3.2025</v>
       </c>
       <c r="G24" t="n">
         <v>-5.3374</v>
@@ -2326,13 +2326,13 @@
         <v>1.3648</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4534</v>
+        <v>-1.0386</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0774</v>
+        <v>-0.7272</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.376</v>
+        <v>-0.3114</v>
       </c>
       <c r="V24" t="n">
         <v>-0.5451</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-28.3339</v>
+        <v>-28.3338</v>
       </c>
       <c r="E25" t="n">
         <v>-21.1984</v>
       </c>
       <c r="F25" t="n">
-        <v>-7.1354</v>
+        <v>-7.135299999999999</v>
       </c>
       <c r="G25" t="n">
         <v>-21.5176</v>
@@ -2404,13 +2404,13 @@
         <v>13.6484</v>
       </c>
       <c r="S25" t="n">
-        <v>-7.542400000000001</v>
+        <v>-7.5426</v>
       </c>
       <c r="T25" t="n">
         <v>-7.601</v>
       </c>
       <c r="U25" t="n">
-        <v>0.05859999999999999</v>
+        <v>0.0585</v>
       </c>
       <c r="V25" t="n">
         <v>1.8636</v>
